--- a/resources/templates/sq_gap_forms/04_지그치공구_점검체크시트_L1200-03.xlsx
+++ b/resources/templates/sq_gap_forms/04_지그치공구_점검체크시트_L1200-03.xlsx
@@ -21,7 +21,7 @@
     <t>용접 지그 기준핀 정기(분기) 측정 기록</t>
   </si>
   <si>
-    <t>양식번호: L1200-03(제안)   Rev.0   제정일: 2026-07-16   SQ 연계항목: 3_7   ※ 노란색 셀에 기록하세요. 회색 기울임 행은 작성 예시입니다.</t>
+    <t>양식번호: L1200-12   Rev.0   제정일: 2026-07-16   SQ 연계항목: 3_7   ※ 노란색 셀에 기록하세요. 회색 기울임 행은 작성 예시입니다.</t>
   </si>
   <si>
     <t>측정일</t>
@@ -1192,7 +1192,7 @@
     <mergeCell ref="F3:J3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 
